--- a/docs/StructureDefinition-DIPSHealthcareService.xlsx
+++ b/docs/StructureDefinition-DIPSHealthcareService.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -437,7 +437,7 @@
     <t>ward</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceWard}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceWard}
 </t>
   </si>
   <si>
@@ -500,7 +500,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceWard</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceWard</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -669,7 +669,7 @@
     <t>section</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceSection}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceSection}
 </t>
   </si>
   <si>
@@ -682,7 +682,7 @@
     <t>HealthcareService.extension:section.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceSection</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceSection</t>
   </si>
   <si>
     <t>HealthcareService.extension:section.value[x]</t>
@@ -718,7 +718,7 @@
     <t>department</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceDepartment}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceDepartment}
 </t>
   </si>
   <si>
@@ -731,7 +731,7 @@
     <t>HealthcareService.extension:department.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceDepartment</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceDepartment</t>
   </si>
   <si>
     <t>HealthcareService.extension:department.value[x]</t>
@@ -767,7 +767,7 @@
     <t>hospital</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceHospital}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceHospital}
 </t>
   </si>
   <si>
@@ -780,7 +780,7 @@
     <t>HealthcareService.extension:hospital.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceHospital</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceHospital</t>
   </si>
   <si>
     <t>HealthcareService.extension:hospital.value[x]</t>
@@ -816,7 +816,7 @@
     <t>address</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceAddress}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceAddress}
 </t>
   </si>
   <si>
@@ -829,7 +829,7 @@
     <t>HealthcareService.extension:address.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceAddress</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceAddress</t>
   </si>
   <si>
     <t>HealthcareService.extension:address.value[x]</t>
@@ -2532,7 +2532,7 @@
     <t>communicationProtocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceCommunicationProtocol}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceCommunicationProtocol}
 </t>
   </si>
   <si>
@@ -2554,7 +2554,7 @@
     <t>HealthcareService.communication.coding.extension.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceCommunicationProtocol</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceCommunicationProtocol</t>
   </si>
   <si>
     <t>HealthcareService.communication.coding.extension:communicationProtocol.value[x]</t>
@@ -2614,7 +2614,7 @@
     <t>isPaperCopy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSHealthcareServiceIsPaperCopy}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSHealthcareServiceIsPaperCopy}
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-DIPSHealthcareService.xlsx
+++ b/docs/StructureDefinition-DIPSHealthcareService.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSHealthcareService.xlsx
+++ b/docs/StructureDefinition-DIPSHealthcareService.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSHealthcareService.xlsx
+++ b/docs/StructureDefinition-DIPSHealthcareService.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSHealthcareService.xlsx
+++ b/docs/StructureDefinition-DIPSHealthcareService.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSHealthcareService.xlsx
+++ b/docs/StructureDefinition-DIPSHealthcareService.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
